--- a/data/print_templates/D__destination_label__all_labels.xlsx
+++ b/data/print_templates/D__destination_label__all_labels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/EdouardGonnu/asf-wms/data/print_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D53D99-D73D-0D4D-8AD0-729C6E2770F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD762A35-7EFB-8A47-ABC7-D5E9655DFA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{D41FDF60-E254-7C4C-BFC3-DDF9FE3B5742}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{D41FDF60-E254-7C4C-BFC3-DDF9FE3B5742}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -47,24 +47,17 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>N° COLIS</t>
+    <t>N° du COLIS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="36"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -76,14 +69,27 @@
     </font>
     <font>
       <b/>
-      <sz val="36"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="60"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="60"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -226,64 +232,42 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFFF0000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFFF0000"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thick">
         <color rgb="FFFF0000"/>
       </right>
-      <top style="medium">
+      <top style="thick">
         <color rgb="FFFF0000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thick">
         <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -291,46 +275,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -670,7 +653,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M8"/>
+  <dimension ref="B1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" customWidth="1"/>
@@ -678,46 +661,40 @@
     <col min="7" max="7" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:13" ht="72" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
+    <row r="1" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" ht="72" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
-    <row r="3" spans="2:13" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:13" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
+    <row r="3" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:6" ht="72" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="2"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="2:13" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="2:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+    <row r="5" spans="2:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="2:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:13" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="M8">
-        <f>18*4</f>
-        <v>72</v>
-      </c>
+    <row r="7" spans="2:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
